--- a/samples/예시데이터_표준현황.xlsx
+++ b/samples/예시데이터_표준현황.xlsx
@@ -449,7 +449,7 @@
         <v>장비 점검·TPR 작성(h)</v>
       </c>
       <c r="Q1" t="str">
-        <v>특화 장비수리(h)</v>
+        <v>특화 시험·장비수리(h)</v>
       </c>
       <c r="R1" t="str">
         <v>히터 가동(h)</v>
